--- a/gte/nodes/LPC/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
+++ b/gte/nodes/LPC/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-21.469559016164439</v>
+        <v>-20.124901079266269</v>
       </c>
       <c r="B1">
-        <v>18.646566837756978</v>
+        <v>19.935346134300392</v>
       </c>
       <c r="C1">
         <v>384.89451392788493</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-19.118936951918908</v>
+        <v>-17.857721239776119</v>
       </c>
       <c r="B2">
-        <v>18.57339932838158</v>
+        <v>19.70724294519778</v>
       </c>
       <c r="C2">
         <v>384.89451392788493</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-17.347112190531497</v>
+        <v>-16.182738013024778</v>
       </c>
       <c r="B3">
-        <v>18.022610805674933</v>
+        <v>19.029573721859567</v>
       </c>
       <c r="C3">
         <v>384.89451392788493</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-15.67925637226511</v>
+        <v>-14.609891455592992</v>
       </c>
       <c r="B4">
-        <v>17.386027563947955</v>
+        <v>18.274367450202767</v>
       </c>
       <c r="C4">
         <v>384.89451392788493</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-14.088451638104393</v>
+        <v>-13.111632071726408</v>
       </c>
       <c r="B5">
-        <v>16.685862103217712</v>
+        <v>17.462538328797688</v>
       </c>
       <c r="C5">
         <v>384.89451392788493</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-12.563440143335754</v>
+        <v>-11.676557976253482</v>
       </c>
       <c r="B6">
-        <v>15.931404347907632</v>
+        <v>16.60274209830396</v>
       </c>
       <c r="C6">
         <v>384.89451392788493</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-11.097633098759358</v>
+        <v>-10.298061329273729</v>
       </c>
       <c r="B7">
-        <v>15.128091338167533</v>
+        <v>15.699995100110606</v>
       </c>
       <c r="C7">
         <v>384.89451392788493</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-9.68699555355099</v>
+        <v>-8.9721589709251255</v>
       </c>
       <c r="B8">
-        <v>14.279252697843097</v>
+        <v>14.757321149863284</v>
       </c>
       <c r="C8">
         <v>384.89451392788493</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-8.32551587367483</v>
+        <v>-7.6928005809574289</v>
       </c>
       <c r="B9">
-        <v>13.389849201156631</v>
+        <v>13.779313347931439</v>
       </c>
       <c r="C9">
         <v>384.89451392788493</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-7.0067585049468208</v>
+        <v>-6.4534864266422307</v>
       </c>
       <c r="B10">
-        <v>12.465191439390358</v>
+        <v>12.770905966148849</v>
       </c>
       <c r="C10">
         <v>384.89451392788493</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.7245688958015668</v>
+        <v>-5.2479862857266868</v>
       </c>
       <c r="B11">
-        <v>11.510358121689526</v>
+        <v>11.73682867748286</v>
       </c>
       <c r="C11">
         <v>384.89451392788493</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.4755423593159023</v>
+        <v>-4.0728999866487534</v>
       </c>
       <c r="B12">
-        <v>10.528158780873802</v>
+        <v>10.679662722035118</v>
       </c>
       <c r="C12">
         <v>384.89451392788493</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.2669926645169989</v>
+        <v>-2.9358780501340762</v>
       </c>
       <c r="B13">
-        <v>9.51255812659754</v>
+        <v>9.5936002073110167</v>
       </c>
       <c r="C13">
         <v>384.89451392788493</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.1032177844703388</v>
+        <v>-1.8414480847114239</v>
       </c>
       <c r="B14">
-        <v>8.4600094902071916</v>
+        <v>8.4752039994819146</v>
       </c>
       <c r="C14">
         <v>384.89451392788493</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.96573405244434374</v>
+        <v>-0.770595357834373</v>
       </c>
       <c r="B15">
-        <v>7.3857655129829016</v>
+        <v>7.3389091319793733</v>
       </c>
       <c r="C15">
         <v>384.89451392788493</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>0.16241008714175864</v>
+        <v>0.29411960583501912</v>
       </c>
       <c r="B16">
-        <v>6.303814544756384</v>
+        <v>6.197954781789857</v>
       </c>
       <c r="C16">
         <v>384.89451392788493</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1.2692561054684681</v>
+        <v>1.3402929117256432</v>
       </c>
       <c r="B17">
-        <v>5.20428845963189</v>
+        <v>5.0429245328592005</v>
       </c>
       <c r="C17">
         <v>384.89451392788493</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>2.3393013402979097</v>
+        <v>2.3518688972709931</v>
       </c>
       <c r="B18">
-        <v>4.0743945282535279</v>
+        <v>3.8616297296095481</v>
       </c>
       <c r="C18">
         <v>384.89451392788493</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>3.3717766801190172</v>
+        <v>3.3280281978320385</v>
       </c>
       <c r="B19">
-        <v>2.9134980831522821</v>
+        <v>2.65344835140884</v>
       </c>
       <c r="C19">
         <v>384.89451392788493</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>4.3695964011024309</v>
+        <v>4.2717605232516318</v>
       </c>
       <c r="B20">
-        <v>1.724003972330848</v>
+        <v>1.4206500363614638</v>
       </c>
       <c r="C20">
         <v>384.89451392788493</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>5.3356747794187838</v>
+        <v>5.1860555833726112</v>
       </c>
       <c r="B21">
-        <v>0.50831704379193132</v>
+        <v>0.16550442257181383</v>
       </c>
       <c r="C21">
         <v>384.89451392788493</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.2723998304523212</v>
+        <v>6.07336608035147</v>
       </c>
       <c r="B22">
-        <v>-0.73159212257055062</v>
+        <v>-1.1101265212187677</v>
       </c>
       <c r="C22">
         <v>384.89451392788493</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.1800545264416868</v>
+        <v>6.9339966855992454</v>
       </c>
       <c r="B23">
-        <v>-1.9954900192977574</v>
+        <v>-2.4060115037210963</v>
       </c>
       <c r="C23">
         <v>384.89451392788493</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>8.0583955788391375</v>
+        <v>7.7677150628406286</v>
       </c>
       <c r="B24">
-        <v>-3.2835774070396342</v>
+        <v>-3.7223269030090305</v>
       </c>
       <c r="C24">
         <v>384.89451392788493</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>8.9071796990969219</v>
+        <v>8.5742888758003026</v>
       </c>
       <c r="B25">
-        <v>-4.5960550464461258</v>
+        <v>-5.0592490971564343</v>
       </c>
       <c r="C25">
         <v>384.89451392788493</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>9.7260630007165929</v>
+        <v>9.35338848220681</v>
       </c>
       <c r="B26">
-        <v>-5.933206711157923</v>
+        <v>-6.4170283340801371</v>
       </c>
       <c r="C26">
         <v>384.89451392788493</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>10.514299205396874</v>
+        <v>10.104295015804123</v>
       </c>
       <c r="B27">
-        <v>-7.2956482267787992</v>
+        <v>-7.79621034106889</v>
       </c>
       <c r="C27">
         <v>384.89451392788493</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>11.271041436885779</v>
+        <v>10.826192304340063</v>
       </c>
       <c r="B28">
-        <v>-8.68407843190326</v>
+        <v>-9.1974147152544</v>
       </c>
       <c r="C28">
         <v>384.89451392788493</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>11.995442818931325</v>
+        <v>11.518264175562457</v>
       </c>
       <c r="B29">
-        <v>-10.09919616512582</v>
+        <v>-10.621261053768384</v>
       </c>
       <c r="C29">
         <v>384.89451392788493</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>12.687017394884729</v>
+        <v>12.180074970203526</v>
       </c>
       <c r="B30">
-        <v>-11.541402435756439</v>
+        <v>-12.068080087326074</v>
       </c>
       <c r="C30">
         <v>384.89451392788493</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>13.346722886510044</v>
+        <v>12.812711080933099</v>
       </c>
       <c r="B31">
-        <v>-13.009906935966836</v>
+        <v>-13.537047080976791</v>
       </c>
       <c r="C31">
         <v>384.89451392788493</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>13.975877935174522</v>
+        <v>13.417639413405405</v>
       </c>
       <c r="B32">
-        <v>-14.503621528644183</v>
+        <v>-15.027048433353393</v>
       </c>
       <c r="C32">
         <v>384.89451392788493</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>14.575801182245417</v>
+        <v>13.996326873274676</v>
       </c>
       <c r="B33">
-        <v>-16.021458076675646</v>
+        <v>-16.536970543088724</v>
       </c>
       <c r="C33">
         <v>384.89451392788493</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>15.147173459971167</v>
+        <v>14.549592599189385</v>
       </c>
       <c r="B34">
-        <v>-17.56285476025522</v>
+        <v>-18.066191561111438</v>
       </c>
       <c r="C34">
         <v>384.89451392788493</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>15.688124364124919</v>
+        <v>15.075664661775022</v>
       </c>
       <c r="B35">
-        <v>-19.129355028804245</v>
+        <v>-19.616056647533409</v>
       </c>
       <c r="C35">
         <v>384.89451392788493</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>16.196145681360996</v>
+        <v>15.572123364651318</v>
       </c>
       <c r="B36">
-        <v>-20.723028649050878</v>
+        <v>-21.188402714762322</v>
       </c>
       <c r="C36">
         <v>384.89451392788493</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>16.668729198333736</v>
+        <v>16.036549011438009</v>
       </c>
       <c r="B37">
-        <v>-22.345945387723308</v>
+        <v>-22.785066675205872</v>
       </c>
       <c r="C37">
         <v>384.89451392788493</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>17.101834177352785</v>
+        <v>16.464952773786035</v>
       </c>
       <c r="B38">
-        <v>-24.00143964396392</v>
+        <v>-24.409076647741411</v>
       </c>
       <c r="C38">
         <v>384.89451392788493</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>17.485289783349092</v>
+        <v>16.847069295471133</v>
       </c>
       <c r="B39">
-        <v>-25.697904346572006</v>
+        <v>-26.06822557712491</v>
       </c>
       <c r="C39">
         <v>384.89451392788493</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>17.807392656908917</v>
+        <v>17.171064088300248</v>
       </c>
       <c r="B40">
-        <v>-27.444997056761075</v>
+        <v>-27.771497614582024</v>
       </c>
       <c r="C40">
         <v>384.89451392788493</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>18.056439438618515</v>
+        <v>17.425102664080335</v>
       </c>
       <c r="B41">
-        <v>-29.25237533574462</v>
+        <v>-29.527876911338389</v>
       </c>
       <c r="C41">
         <v>384.89451392788493</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>18.056439438618515</v>
+        <v>17.425102664080335</v>
       </c>
       <c r="B42">
-        <v>-29.25237533574462</v>
+        <v>-29.527876911338389</v>
       </c>
       <c r="C42">
         <v>384.89451392788493</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>17.281836182962007</v>
+        <v>16.628344021544851</v>
       </c>
       <c r="B43">
-        <v>-27.8786839699685</v>
+        <v>-28.183503530966622</v>
       </c>
       <c r="C43">
         <v>384.89451392788493</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>16.524437003348652</v>
+        <v>15.854837041175619</v>
       </c>
       <c r="B44">
-        <v>-26.490795875574946</v>
+        <v>-26.821478652216442</v>
       </c>
       <c r="C44">
         <v>384.89451392788493</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>15.773701589185192</v>
+        <v>15.093446108675211</v>
       </c>
       <c r="B45">
-        <v>-25.097408870956592</v>
+        <v>-25.450255876224322</v>
       </c>
       <c r="C45">
         <v>384.89451392788493</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>15.019089629878339</v>
+        <v>14.33303560974621</v>
       </c>
       <c r="B46">
-        <v>-23.707220774506034</v>
+        <v>-24.078288804126732</v>
       </c>
       <c r="C46">
         <v>384.89451392788493</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>14.251537242163014</v>
+        <v>13.564008015964284</v>
       </c>
       <c r="B47">
-        <v>-22.327711063215315</v>
+        <v>-22.712863399232788</v>
       </c>
       <c r="C47">
         <v>384.89451392788493</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>13.467886252086906</v>
+        <v>12.782918142397433</v>
       </c>
       <c r="B48">
-        <v>-20.961485848474272</v>
+        <v>-21.35659507354211</v>
       </c>
       <c r="C48">
         <v>384.89451392788493</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>12.666454913025879</v>
+        <v>11.987858889986731</v>
       </c>
       <c r="B49">
-        <v>-19.609932900272167</v>
+        <v>-20.010931601226925</v>
       </c>
       <c r="C49">
         <v>384.89451392788493</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>11.845561478355828</v>
+        <v>11.176923159673265</v>
       </c>
       <c r="B50">
-        <v>-18.274439988598274</v>
+        <v>-18.677320756459483</v>
       </c>
       <c r="C50">
         <v>384.89451392788493</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>11.004112904624211</v>
+        <v>10.348822653049927</v>
       </c>
       <c r="B51">
-        <v>-16.955909088148815</v>
+        <v>-17.356740550922616</v>
       </c>
       <c r="C51">
         <v>384.89451392788493</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>10.143370961064816</v>
+        <v>9.5047442743168649</v>
       </c>
       <c r="B52">
-        <v>-15.653298992447777</v>
+        <v>-16.048289946341544</v>
       </c>
       <c r="C52">
         <v>384.89451392788493</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>9.26518612008302</v>
+        <v>8.6464937283260461</v>
       </c>
       <c r="B53">
-        <v>-14.365082699726095</v>
+        <v>-14.750598141952072</v>
       </c>
       <c r="C53">
         <v>384.89451392788493</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>8.3714088540841942</v>
+        <v>7.7758767199294274</v>
       </c>
       <c r="B54">
-        <v>-13.089733208214698</v>
+        <v>-13.462294336989986</v>
       </c>
       <c r="C54">
         <v>384.89451392788493</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>7.4634904587295976</v>
+        <v>6.8942945474336836</v>
       </c>
       <c r="B55">
-        <v>-11.826052915055122</v>
+        <v>-12.182314735903349</v>
       </c>
       <c r="C55">
         <v>384.89451392788493</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>6.54128552270406</v>
+        <v>6.0015308829643352</v>
       </c>
       <c r="B56">
-        <v>-10.574161813031298</v>
+        <v>-10.910823563989181</v>
       </c>
       <c r="C56">
         <v>384.89451392788493</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5.6042494579482991</v>
+        <v>5.0969649921016122</v>
       </c>
       <c r="B57">
-        <v>-9.3345092938377583</v>
+        <v>-9.6482920517567567</v>
       </c>
       <c r="C57">
         <v>384.89451392788493</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4.6518376764030416</v>
+        <v>4.1799761404257554</v>
       </c>
       <c r="B58">
-        <v>-8.1075447491690422</v>
+        <v>-8.3951914297153465</v>
       </c>
       <c r="C58">
         <v>384.89451392788493</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.6835723390199338</v>
+        <v>3.250019099689839</v>
       </c>
       <c r="B59">
-        <v>-6.893662489726573</v>
+        <v>-7.1519356078661893</v>
       </c>
       <c r="C59">
         <v>384.89451392788493</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.6992426027943877</v>
+        <v>2.3068506663383856</v>
       </c>
       <c r="B60">
-        <v>-5.6930365022394049</v>
+        <v>-5.9187092141784481</v>
       </c>
       <c r="C60">
         <v>384.89451392788493</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.6987043737327512</v>
+        <v>1.3503031429887651</v>
       </c>
       <c r="B61">
-        <v>-4.5057856924434914</v>
+        <v>-4.695639556113254</v>
       </c>
       <c r="C61">
         <v>384.89451392788493</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.681813557841368</v>
+        <v>0.38020883225834745</v>
       </c>
       <c r="B62">
-        <v>-3.3320289660747808</v>
+        <v>-3.4828539411317423</v>
       </c>
       <c r="C62">
         <v>384.89451392788493</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.35108144915445533</v>
+        <v>-0.60308495012165209</v>
       </c>
       <c r="B63">
-        <v>-2.1714788284982252</v>
+        <v>-2.2800887045108378</v>
       </c>
       <c r="C63">
         <v>384.89451392788493</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.3976622926536164</v>
+        <v>-1.5971708359646812</v>
       </c>
       <c r="B64">
-        <v>-1.0222221835947158</v>
+        <v>-1.0855162927905913</v>
       </c>
       <c r="C64">
         <v>384.89451392788493</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.4551181283360477</v>
+        <v>-2.5991264439703392</v>
       </c>
       <c r="B65">
-        <v>0.11806046512585289</v>
+        <v>0.10308181967314738</v>
       </c>
       <c r="C65">
         <v>384.89451392788493</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.5206381118816918</v>
+        <v>-3.6060293928382343</v>
       </c>
       <c r="B66">
-        <v>1.2516886141535943</v>
+        <v>1.2879241585245402</v>
       </c>
       <c r="C66">
         <v>384.89451392788493</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-4.595122708786743</v>
+        <v>-4.6187844198855537</v>
       </c>
       <c r="B67">
-        <v>2.3779192032830787</v>
+        <v>2.4683238924664028</v>
       </c>
       <c r="C67">
         <v>384.89451392788493</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-5.6943176238124229</v>
+        <v>-5.6536047368998341</v>
       </c>
       <c r="B68">
-        <v>3.4837589455267275</v>
+        <v>3.6319727624361957</v>
       </c>
       <c r="C68">
         <v>384.89451392788493</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-6.830465866506</v>
+        <v>-6.7230783601113959</v>
       </c>
       <c r="B69">
-        <v>4.5591049627313236</v>
+        <v>4.7693145764297453</v>
       </c>
       <c r="C69">
         <v>384.89451392788493</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-7.9869544262938463</v>
+        <v>-7.809984049051323</v>
       </c>
       <c r="B70">
-        <v>5.6176662388632277</v>
+        <v>5.8934228384416416</v>
       </c>
       <c r="C70">
         <v>384.89451392788493</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-9.1456721830220111</v>
+        <v>-8.8955466389553539</v>
       </c>
       <c r="B71">
-        <v>6.6743879913893913</v>
+        <v>7.0185507140314733</v>
       </c>
       <c r="C71">
         <v>384.89451392788493</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-10.311371598336081</v>
+        <v>-9.9845845245770573</v>
       </c>
       <c r="B72">
-        <v>7.7253485096595105</v>
+        <v>8.1410403190199876</v>
       </c>
       <c r="C72">
         <v>384.89451392788493</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-11.491862376626484</v>
+        <v>-11.085064560125073</v>
       </c>
       <c r="B73">
-        <v>8.764103259626248</v>
+        <v>9.2548436163619332</v>
       </c>
       <c r="C73">
         <v>384.89451392788493</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-12.684319611463474</v>
+        <v>-12.193953878110559</v>
       </c>
       <c r="B74">
-        <v>9.79298334177138</v>
+        <v>10.362263007286897</v>
       </c>
       <c r="C74">
         <v>384.89451392788493</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-13.883212977881838</v>
+        <v>-13.305416220236509</v>
       </c>
       <c r="B75">
-        <v>10.816552356168529</v>
+        <v>11.467729087041311</v>
       </c>
       <c r="C75">
         <v>384.89451392788493</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-15.082825087594692</v>
+        <v>-14.413401486670875</v>
       </c>
       <c r="B76">
-        <v>11.839528266729589</v>
+        <v>12.575834788664166</v>
       </c>
       <c r="C76">
         <v>384.89451392788493</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-16.27791405409744</v>
+        <v>-15.512338960303136</v>
       </c>
       <c r="B77">
-        <v>12.866236655366814</v>
+        <v>13.690809121821106</v>
       </c>
       <c r="C77">
         <v>384.89451392788493</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-17.465327061336257</v>
+        <v>-16.598789296443943</v>
       </c>
       <c r="B78">
-        <v>13.899279212155513</v>
+        <v>14.815263064891751</v>
       </c>
       <c r="C78">
         <v>384.89451392788493</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-18.639410998587511</v>
+        <v>-17.666718639813467</v>
       </c>
       <c r="B79">
-        <v>14.943320859442368</v>
+        <v>15.95377721886395</v>
       </c>
       <c r="C79">
         <v>384.89451392788493</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-19.789958241380077</v>
+        <v>-18.705362388352356</v>
       </c>
       <c r="B80">
-        <v>16.006784884481004</v>
+        <v>17.114523530948887</v>
       </c>
       <c r="C80">
         <v>384.89451392788493</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-20.891197812338469</v>
+        <v>-19.687860492464754</v>
       </c>
       <c r="B81">
-        <v>17.110937385554614</v>
+        <v>18.317892806693958</v>
       </c>
       <c r="C81">
         <v>384.89451392788493</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-21.469559016164439</v>
+        <v>-20.124901079266269</v>
       </c>
       <c r="B82">
-        <v>18.646566837756978</v>
+        <v>19.935346134300392</v>
       </c>
       <c r="C82">
         <v>384.89451392788493</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-28.864314499905621</v>
+        <v>-28.270656294512882</v>
       </c>
       <c r="B1">
-        <v>15.216595529206684</v>
+        <v>16.233396263651514</v>
       </c>
       <c r="C1">
         <v>452.5754307907855</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-26.897068663385223</v>
+        <v>-26.342590146990052</v>
       </c>
       <c r="B2">
-        <v>14.969706398357243</v>
+        <v>15.892737356202638</v>
       </c>
       <c r="C2">
         <v>452.5754307907855</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-25.11276313336765</v>
+        <v>-24.6019833520704</v>
       </c>
       <c r="B3">
-        <v>14.427983233547337</v>
+        <v>15.264055641150623</v>
       </c>
       <c r="C3">
         <v>452.5754307907855</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-23.360892263431861</v>
+        <v>-22.893136946570351</v>
       </c>
       <c r="B4">
-        <v>13.833987052173413</v>
+        <v>14.586575525783141</v>
       </c>
       <c r="C4">
         <v>452.5754307907855</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-21.633066734067622</v>
+        <v>-21.207386723457702</v>
       </c>
       <c r="B5">
-        <v>13.201238422560026</v>
+        <v>13.873609171912477</v>
       </c>
       <c r="C5">
         <v>452.5754307907855</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-19.925852917469836</v>
+        <v>-19.541194763457128</v>
       </c>
       <c r="B6">
-        <v>12.535271118845001</v>
+        <v>13.13059243231735</v>
       </c>
       <c r="C6">
         <v>452.5754307907855</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-18.237282850838486</v>
+        <v>-17.89253834314723</v>
       </c>
       <c r="B7">
-        <v>11.839256789868946</v>
+        <v>12.360633129951106</v>
       </c>
       <c r="C7">
         <v>452.5754307907855</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-16.56619158167133</v>
+        <v>-16.260224950410368</v>
       </c>
       <c r="B8">
-        <v>11.115072920436434</v>
+        <v>11.565563505688653</v>
       </c>
       <c r="C8">
         <v>452.5754307907855</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-14.910771525917177</v>
+        <v>-14.642395895191013</v>
       </c>
       <c r="B9">
-        <v>10.3656326864775</v>
+        <v>10.748239352643653</v>
       </c>
       <c r="C9">
         <v>452.5754307907855</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-13.269073581049245</v>
+        <v>-13.037045442820938</v>
       </c>
       <c r="B10">
-        <v>9.5940773408497488</v>
+        <v>9.9117423913194056</v>
       </c>
       <c r="C10">
         <v>452.5754307907855</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-11.639225202187378</v>
+        <v>-11.442245858118968</v>
       </c>
       <c r="B11">
-        <v>8.8034247529956424</v>
+        <v>9.0590344995389387</v>
       </c>
       <c r="C11">
         <v>452.5754307907855</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-10.020220514222009</v>
+        <v>-9.8569654838623944</v>
       </c>
       <c r="B12">
-        <v>7.9952960321276922</v>
+        <v>8.1917007719141921</v>
       </c>
       <c r="C12">
         <v>452.5754307907855</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-8.4144437634793317</v>
+        <v>-8.2836789751752882</v>
       </c>
       <c r="B13">
-        <v>7.1658486299538229</v>
+        <v>7.3059390128929822</v>
       </c>
       <c r="C13">
         <v>452.5754307907855</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-6.82331678707354</v>
+        <v>-6.7238646663325321</v>
       </c>
       <c r="B14">
-        <v>6.3127910559871809</v>
+        <v>6.39947782879708</v>
       </c>
       <c r="C14">
         <v>452.5754307907855</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-5.24102166383511</v>
+        <v>-5.1715092958654925</v>
       </c>
       <c r="B15">
-        <v>5.4454997084664312</v>
+        <v>5.4815563236082063</v>
       </c>
       <c r="C15">
         <v>452.5754307907855</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.6622222441264487</v>
+        <v>-3.6210975357212325</v>
       </c>
       <c r="B16">
-        <v>4.572574543046759</v>
+        <v>4.5606485491600068</v>
       </c>
       <c r="C16">
         <v>452.5754307907855</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.0907492227213353</v>
+        <v>-2.076597387253083</v>
       </c>
       <c r="B17">
-        <v>3.6878418563239266</v>
+        <v>3.6306578510338423</v>
       </c>
       <c r="C17">
         <v>452.5754307907855</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.53155264790229351</v>
+        <v>-0.54313428484316273</v>
       </c>
       <c r="B18">
-        <v>2.7833239492805215</v>
+        <v>2.6837092313679314</v>
       </c>
       <c r="C18">
         <v>452.5754307907855</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1.0151068624246533</v>
+        <v>0.97901993441759649</v>
       </c>
       <c r="B19">
-        <v>1.8586007995058353</v>
+        <v>1.7193850247801448</v>
       </c>
       <c r="C19">
         <v>452.5754307907855</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.5501410479476236</v>
+        <v>2.4908068327610779</v>
       </c>
       <c r="B20">
-        <v>0.91514180374082543</v>
+        <v>0.7391318990082596</v>
       </c>
       <c r="C20">
         <v>452.5754307907855</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.07446164835471</v>
+        <v>3.9931679724191405</v>
       </c>
       <c r="B21">
-        <v>-0.045583641273538693</v>
+        <v>-0.25560347820993551</v>
       </c>
       <c r="C21">
         <v>452.5754307907855</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>5.5888176601338015</v>
+        <v>5.48687710721529</v>
       </c>
       <c r="B22">
-        <v>-1.0223684223528367</v>
+        <v>-1.2636322691582089</v>
       </c>
       <c r="C22">
         <v>452.5754307907855</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.09330710697185</v>
+        <v>6.9720367573395</v>
       </c>
       <c r="B23">
-        <v>-2.0150545605387795</v>
+        <v>-2.284796956206502</v>
       </c>
       <c r="C23">
         <v>452.5754307907855</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>8.58786526935558</v>
+        <v>8.4485816345733653</v>
       </c>
       <c r="B24">
-        <v>-3.0237463604296155</v>
+        <v>-3.3191978517462979</v>
       </c>
       <c r="C24">
         <v>452.5754307907855</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>10.07242742777173</v>
+        <v>9.9164464506985</v>
       </c>
       <c r="B25">
-        <v>-4.0485481266236016</v>
+        <v>-4.3669352681690921</v>
       </c>
       <c r="C25">
         <v>452.5754307907855</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>11.546901238842258</v>
+        <v>11.375537889511458</v>
       </c>
       <c r="B26">
-        <v>-5.0896086834622576</v>
+        <v>-5.4281525815963461</v>
       </c>
       <c r="C26">
         <v>452.5754307907855</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>13.011083863730111</v>
+        <v>12.82565052286864</v>
       </c>
       <c r="B27">
-        <v>-6.1472549342602312</v>
+        <v>-6.5031654230694622</v>
       </c>
       <c r="C27">
         <v>452.5754307907855</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>14.464744839733447</v>
+        <v>14.266550894641396</v>
       </c>
       <c r="B28">
-        <v>-7.2218583020754252</v>
+        <v>-7.5923324873598048</v>
       </c>
       <c r="C28">
         <v>452.5754307907855</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>15.907653704150453</v>
+        <v>15.698005548701099</v>
       </c>
       <c r="B29">
-        <v>-8.3137902099657612</v>
+        <v>-8.6960124692387542</v>
       </c>
       <c r="C29">
         <v>452.5754307907855</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>17.3396994909728</v>
+        <v>17.119905233798153</v>
       </c>
       <c r="B30">
-        <v>-9.42322949526071</v>
+        <v>-9.8143732283046869</v>
       </c>
       <c r="C30">
         <v>452.5754307907855</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>18.761249220966143</v>
+        <v>18.532637518199184</v>
       </c>
       <c r="B31">
-        <v>-10.549584652375955</v>
+        <v>-10.946819283463984</v>
       </c>
       <c r="C31">
         <v>452.5754307907855</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>20.172789411589676</v>
+        <v>19.936714175049907</v>
       </c>
       <c r="B32">
-        <v>-11.692071589998781</v>
+        <v>-12.092564318450064</v>
       </c>
       <c r="C32">
         <v>452.5754307907855</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>21.57480658030255</v>
+        <v>21.332646977496012</v>
       </c>
       <c r="B33">
-        <v>-12.849906216816429</v>
+        <v>-13.25082201699631</v>
       </c>
       <c r="C33">
         <v>452.5754307907855</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>22.967591462211683</v>
+        <v>22.720745762768619</v>
       </c>
       <c r="B34">
-        <v>-14.02261997231307</v>
+        <v>-14.421116328225715</v>
       </c>
       <c r="C34">
         <v>452.5754307907855</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>24.350651663014876</v>
+        <v>24.100512624440615</v>
       </c>
       <c r="B35">
-        <v>-15.211006419160523</v>
+        <v>-15.604212262819655</v>
       </c>
       <c r="C35">
         <v>452.5754307907855</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>25.723299006057676</v>
+        <v>25.471247720170282</v>
       </c>
       <c r="B36">
-        <v>-16.416174650827504</v>
+        <v>-16.801185096849093</v>
       </c>
       <c r="C36">
         <v>452.5754307907855</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>27.084845314685644</v>
+        <v>26.832251207615968</v>
       </c>
       <c r="B37">
-        <v>-17.639233760782766</v>
+        <v>-18.013110106385</v>
       </c>
       <c r="C37">
         <v>452.5754307907855</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>28.434123904052903</v>
+        <v>28.182328764996928</v>
       </c>
       <c r="B38">
-        <v>-18.88206402574632</v>
+        <v>-19.241822312767678</v>
       </c>
       <c r="C38">
         <v>452.5754307907855</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>29.768054056547872</v>
+        <v>29.518308152776335</v>
       </c>
       <c r="B39">
-        <v>-20.149630455443326</v>
+        <v>-20.49219571841471</v>
       </c>
       <c r="C39">
         <v>452.5754307907855</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>31.083076546367561</v>
+        <v>30.836522651978328</v>
       </c>
       <c r="B40">
-        <v>-21.44766924285026</v>
+        <v>-21.769864071013014</v>
       </c>
       <c r="C40">
         <v>452.5754307907855</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>32.375632147708963</v>
+        <v>32.133305543627039</v>
       </c>
       <c r="B41">
-        <v>-22.781916580943566</v>
+        <v>-23.0804611182495</v>
       </c>
       <c r="C41">
         <v>452.5754307907855</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>32.375632147708963</v>
+        <v>32.133305543627039</v>
       </c>
       <c r="B42">
-        <v>-22.781916580943566</v>
+        <v>-23.0804611182495</v>
       </c>
       <c r="C42">
         <v>452.5754307907855</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>30.916305731534095</v>
+        <v>30.663978947876952</v>
       </c>
       <c r="B43">
-        <v>-21.716443866792773</v>
+        <v>-22.034969660034886</v>
       </c>
       <c r="C43">
         <v>452.5754307907855</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>29.463153995376025</v>
+        <v>29.20285376114396</v>
       </c>
       <c r="B44">
-        <v>-20.641019787343787</v>
+        <v>-20.976877108203944</v>
       </c>
       <c r="C44">
         <v>452.5754307907855</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>28.012677751421244</v>
+        <v>27.746293956826474</v>
       </c>
       <c r="B45">
-        <v>-19.56128377590888</v>
+        <v>-19.911770053000215</v>
       </c>
       <c r="C45">
         <v>452.5754307907855</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>26.561377811856214</v>
+        <v>26.290663508322897</v>
       </c>
       <c r="B46">
-        <v>-18.48287526580031</v>
+        <v>-18.845235084667216</v>
       </c>
       <c r="C46">
         <v>452.5754307907855</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>25.106231288288804</v>
+        <v>24.832819768543715</v>
       </c>
       <c r="B47">
-        <v>-17.410666066822628</v>
+        <v>-17.782100738167127</v>
       </c>
       <c r="C47">
         <v>452.5754307907855</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>23.646120490012347</v>
+        <v>23.371593608447714</v>
       </c>
       <c r="B48">
-        <v>-16.346457494749643</v>
+        <v>-16.724163327336651</v>
       </c>
       <c r="C48">
         <v>452.5754307907855</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>22.180404025741549</v>
+        <v>21.906309278505741</v>
       </c>
       <c r="B49">
-        <v>-15.291283241847413</v>
+        <v>-15.672461110731128</v>
       </c>
       <c r="C49">
         <v>452.5754307907855</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>20.708440504191127</v>
+        <v>20.436291029188666</v>
       </c>
       <c r="B50">
-        <v>-14.246177000382041</v>
+        <v>-14.628032346905899</v>
       </c>
       <c r="C50">
         <v>452.5754307907855</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>19.229781951484572</v>
+        <v>18.961063847237796</v>
       </c>
       <c r="B51">
-        <v>-13.211860743261775</v>
+        <v>-13.591606872225585</v>
       </c>
       <c r="C51">
         <v>452.5754307907855</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>17.744754063380448</v>
+        <v>17.48095566447623</v>
       </c>
       <c r="B52">
-        <v>-12.187809565963507</v>
+        <v>-12.562680834291884</v>
       </c>
       <c r="C52">
         <v>452.5754307907855</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>16.253875953046112</v>
+        <v>15.996495148997539</v>
       </c>
       <c r="B53">
-        <v>-11.173186844606294</v>
+        <v>-11.540441958515778</v>
       </c>
       <c r="C53">
         <v>452.5754307907855</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>14.757666733648868</v>
+        <v>14.508210968895247</v>
       </c>
       <c r="B54">
-        <v>-10.16715595530917</v>
+        <v>-10.524077970308222</v>
       </c>
       <c r="C54">
         <v>452.5754307907855</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>13.256523819491193</v>
+        <v>13.016506452429391</v>
       </c>
       <c r="B55">
-        <v>-9.1690764090285484</v>
+        <v>-9.5129691740593536</v>
       </c>
       <c r="C55">
         <v>452.5754307907855</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>11.750357829416029</v>
+        <v>11.521283568525872</v>
       </c>
       <c r="B56">
-        <v>-8.1790922560702466</v>
+        <v>-8.5072661900759474</v>
       </c>
       <c r="C56">
         <v>452.5754307907855</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>10.238957683401418</v>
+        <v>10.022318946277038</v>
       </c>
       <c r="B57">
-        <v>-7.1975436815774172</v>
+        <v>-7.5073122176439275</v>
       </c>
       <c r="C57">
         <v>452.5754307907855</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>8.72211230142543</v>
+        <v>8.5193892147752663</v>
       </c>
       <c r="B58">
-        <v>-6.2247708706932325</v>
+        <v>-6.513450456049231</v>
       </c>
       <c r="C58">
         <v>452.5754307907855</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>7.1996360825323151</v>
+        <v>7.0122979162542052</v>
       </c>
       <c r="B59">
-        <v>-5.2610729454621028</v>
+        <v>-5.5259827537547377</v>
       </c>
       <c r="C59">
         <v>452.5754307907855</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5.671445342031161</v>
+        <v>5.5009562455127092</v>
       </c>
       <c r="B60">
-        <v>-4.3065847755334694</v>
+        <v>-4.5450455559311624</v>
       </c>
       <c r="C60">
         <v>452.5754307907855</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4.1374818742972375</v>
+        <v>3.9853023104909062</v>
       </c>
       <c r="B61">
-        <v>-3.3614001674580147</v>
+        <v>-3.5707339569261616</v>
       </c>
       <c r="C61">
         <v>452.5754307907855</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2.5976874737058311</v>
+        <v>2.46527421912894</v>
       </c>
       <c r="B62">
-        <v>-2.4256129277864318</v>
+        <v>-2.6031430510874047</v>
       </c>
       <c r="C62">
         <v>452.5754307907855</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.0521644637353795</v>
+        <v>0.94097673356052924</v>
       </c>
       <c r="B63">
-        <v>-1.4990581478417273</v>
+        <v>-1.6421118761398044</v>
       </c>
       <c r="C63">
         <v>452.5754307907855</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.49834271572309485</v>
+        <v>-0.5868187673063372</v>
       </c>
       <c r="B64">
-        <v>-0.58053605803614872</v>
+        <v>-0.68645524331723906</v>
       </c>
       <c r="C64">
         <v>452.5754307907855</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.0529290956753945</v>
+        <v>-2.1171742503700752</v>
       </c>
       <c r="B65">
-        <v>0.33141182644572847</v>
+        <v>0.265268092769152</v>
       </c>
       <c r="C65">
         <v>452.5754307907855</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.6106897071273458</v>
+        <v>-3.6491516825291237</v>
       </c>
       <c r="B66">
-        <v>1.2382439904193432</v>
+        <v>1.2144993775082453</v>
       </c>
       <c r="C66">
         <v>452.5754307907855</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-5.1718937262706692</v>
+        <v>-5.1830273599862995</v>
       </c>
       <c r="B67">
-        <v>2.1395266185928636</v>
+        <v>2.1608140942943734</v>
       </c>
       <c r="C67">
         <v>452.5754307907855</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-6.7415069100407239</v>
+        <v>-6.723934896162</v>
       </c>
       <c r="B68">
-        <v>3.0272566952454261</v>
+        <v>3.0963246785437377</v>
       </c>
       <c r="C68">
         <v>452.5754307907855</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-8.3233782526671547</v>
+        <v>-8.2758518165525476</v>
       </c>
       <c r="B69">
-        <v>3.8952310248259434</v>
+        <v>4.0149198424232635</v>
       </c>
       <c r="C69">
         <v>452.5754307907855</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-9.9121931168130146</v>
+        <v>-9.8332739777402978</v>
       </c>
       <c r="B70">
-        <v>4.752014892891447</v>
+        <v>4.9250564530808578</v>
       </c>
       <c r="C70">
         <v>452.5754307907855</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-11.502157079912953</v>
+        <v>-11.390200327998182</v>
       </c>
       <c r="B71">
-        <v>5.6069468263749656</v>
+        <v>5.8359548547831732</v>
       </c>
       <c r="C71">
         <v>452.5754307907855</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-13.094720210054573</v>
+        <v>-12.948123851275305</v>
       </c>
       <c r="B72">
-        <v>6.4576898366054127</v>
+        <v>6.7453211452908262</v>
       </c>
       <c r="C72">
         <v>452.5754307907855</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-14.692297277021256</v>
+        <v>-14.509535029881363</v>
       </c>
       <c r="B73">
-        <v>7.3003521824463791</v>
+        <v>7.649328811297524</v>
       </c>
       <c r="C73">
         <v>452.5754307907855</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-16.293917366726646</v>
+        <v>-16.073420303892213</v>
       </c>
       <c r="B74">
-        <v>8.136498628504329</v>
+        <v>8.54953514173536</v>
       </c>
       <c r="C74">
         <v>452.5754307907855</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-17.897745151582686</v>
+        <v>-17.637871185402627</v>
       </c>
       <c r="B75">
-        <v>8.9690870633209947</v>
+        <v>9.44887244185935</v>
       </c>
       <c r="C75">
         <v>452.5754307907855</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-19.501873333864285</v>
+        <v>-19.200903516816897</v>
       </c>
       <c r="B76">
-        <v>9.8011913654363312</v>
+        <v>10.35038927997781</v>
       </c>
       <c r="C76">
         <v>452.5754307907855</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-21.104538504050481</v>
+        <v>-20.760681382159643</v>
       </c>
       <c r="B77">
-        <v>10.63565351731188</v>
+        <v>11.25690645786141</v>
       </c>
       <c r="C77">
         <v>452.5754307907855</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-22.704624775573858</v>
+        <v>-22.31603750162731</v>
       </c>
       <c r="B78">
-        <v>11.474271927097297</v>
+        <v>12.170217448076931</v>
       </c>
       <c r="C78">
         <v>452.5754307907855</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-24.300215482794773</v>
+        <v>-23.864975501050942</v>
       </c>
       <c r="B79">
-        <v>12.32013557104438</v>
+        <v>13.093389589144325</v>
       </c>
       <c r="C79">
         <v>452.5754307907855</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-25.887932780414715</v>
+        <v>-25.403986042661177</v>
       </c>
       <c r="B80">
-        <v>13.178688321935999</v>
+        <v>14.031814819652569</v>
       </c>
       <c r="C80">
         <v>452.5754307907855</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-27.459446642615447</v>
+        <v>-26.924435236242186</v>
       </c>
       <c r="B81">
-        <v>14.063355187972546</v>
+        <v>14.998758720998167</v>
       </c>
       <c r="C81">
         <v>452.5754307907855</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-28.864314499905621</v>
+        <v>-28.270656294512882</v>
       </c>
       <c r="B82">
-        <v>15.216595529206684</v>
+        <v>16.233396263651514</v>
       </c>
       <c r="C82">
         <v>452.5754307907855</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-33.854446236566154</v>
+        <v>-33.5073107705237</v>
       </c>
       <c r="B1">
-        <v>13.610521878211719</v>
+        <v>14.413711381597436</v>
       </c>
       <c r="C1">
         <v>511.37584442281513</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-31.755750118486489</v>
+        <v>-31.431697447762843</v>
       </c>
       <c r="B2">
-        <v>13.359229027532511</v>
+        <v>14.091095307323251</v>
       </c>
       <c r="C2">
         <v>511.37584442281513</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-29.774604565071222</v>
+        <v>-29.476346854142406</v>
       </c>
       <c r="B3">
-        <v>12.845225961577022</v>
+        <v>13.509631246301288</v>
       </c>
       <c r="C3">
         <v>511.37584442281513</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-27.813073972090919</v>
+        <v>-27.540227836363723</v>
       </c>
       <c r="B4">
-        <v>12.28738601152646</v>
+        <v>12.886774022790791</v>
       </c>
       <c r="C4">
         <v>511.37584442281513</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-25.865713577677912</v>
+        <v>-25.617725893253887</v>
       </c>
       <c r="B5">
-        <v>11.697877511633116</v>
+        <v>12.234608031812432</v>
       </c>
       <c r="C5">
         <v>511.37584442281513</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-23.930302959148531</v>
+        <v>-23.70655272489304</v>
       </c>
       <c r="B6">
-        <v>11.081662817653379</v>
+        <v>11.55805850524451</v>
       </c>
       <c r="C6">
         <v>511.37584442281513</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-22.005574412306167</v>
+        <v>-21.80540270790171</v>
       </c>
       <c r="B7">
-        <v>10.44157508350148</v>
+        <v>10.859935607014277</v>
       </c>
       <c r="C7">
         <v>511.37584442281513</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-20.090782269785272</v>
+        <v>-19.913508679360451</v>
       </c>
       <c r="B8">
-        <v>9.779280778706422</v>
+        <v>10.141890543431703</v>
       </c>
       <c r="C8">
         <v>511.37584442281513</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-18.184761366771703</v>
+        <v>-18.029670507095407</v>
       </c>
       <c r="B9">
-        <v>9.0973838950059438</v>
+        <v>9.406506423987576</v>
       </c>
       <c r="C9">
         <v>511.37584442281513</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-16.286253826160213</v>
+        <v>-16.152592315500442</v>
       </c>
       <c r="B10">
-        <v>8.3986956240438762</v>
+        <v>8.65657243194859</v>
       </c>
       <c r="C10">
         <v>511.37584442281513</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-14.394050419129599</v>
+        <v>-14.281028224494611</v>
       </c>
       <c r="B11">
-        <v>7.6859184348797545</v>
+        <v>7.8947701425042123</v>
       </c>
       <c r="C11">
         <v>511.37584442281513</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-12.507505383221904</v>
+        <v>-12.414313550820657</v>
       </c>
       <c r="B12">
-        <v>6.9604955225746163</v>
+        <v>7.1225301894359605</v>
       </c>
       <c r="C12">
         <v>511.37584442281513</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-10.628178173148092</v>
+        <v>-10.554058402990869</v>
       </c>
       <c r="B13">
-        <v>6.2189417087798962</v>
+        <v>6.3363870489707645</v>
       </c>
       <c r="C13">
         <v>511.37584442281513</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-8.75700130599769</v>
+        <v>-8.7012260210171259</v>
       </c>
       <c r="B14">
-        <v>5.4591729391481163</v>
+        <v>5.53426748745084</v>
       </c>
       <c r="C14">
         <v>511.37584442281513</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-6.8901943312055511</v>
+        <v>-6.8519173791401728</v>
       </c>
       <c r="B15">
-        <v>4.6896380287457458</v>
+        <v>4.7245635892341262</v>
       </c>
       <c r="C15">
         <v>511.37584442281513</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-5.0242898384047612</v>
+        <v>-5.0025563096133849</v>
       </c>
       <c r="B16">
-        <v>3.9180861885318885</v>
+        <v>3.9149725338882453</v>
       </c>
       <c r="C16">
         <v>511.37584442281513</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.161785545675909</v>
+        <v>-3.1557203425118097</v>
       </c>
       <c r="B17">
-        <v>3.1389353436221983</v>
+        <v>3.0999465638038481</v>
       </c>
       <c r="C17">
         <v>511.37584442281513</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.3059070093059648</v>
+        <v>-1.3147377590756781</v>
       </c>
       <c r="B18">
-        <v>2.3449767954540315</v>
+        <v>2.2723220389694312</v>
       </c>
       <c r="C18">
         <v>511.37584442281513</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.54317399004015265</v>
+        <v>0.5202138526157758</v>
       </c>
       <c r="B19">
-        <v>1.5358266365949567</v>
+        <v>1.4317167269418356</v>
       </c>
       <c r="C19">
         <v>511.37584442281513</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.3860491156030372</v>
+        <v>2.349744577773567</v>
       </c>
       <c r="B20">
-        <v>0.71280715739509726</v>
+        <v>0.579443747169995</v>
       </c>
       <c r="C20">
         <v>511.37584442281513</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.223310030623276</v>
+        <v>4.1744645016087043</v>
       </c>
       <c r="B21">
-        <v>-0.1227593517954199</v>
+        <v>-0.28318378089715879</v>
       </c>
       <c r="C21">
         <v>511.37584442281513</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.055443042354276</v>
+        <v>5.9948751170050762</v>
       </c>
       <c r="B22">
-        <v>-0.96978605754798419</v>
+        <v>-1.1550864669590175</v>
       </c>
       <c r="C22">
         <v>511.37584442281513</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.8825130341006382</v>
+        <v>7.8110435475379933</v>
       </c>
       <c r="B23">
-        <v>-1.8281279541200042</v>
+        <v>-2.0361198373082336</v>
       </c>
       <c r="C23">
         <v>511.37584442281513</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>9.70447953317977</v>
+        <v>9.6229283244556321</v>
       </c>
       <c r="B24">
-        <v>-2.6978754926903985</v>
+        <v>-2.92637314738578</v>
       </c>
       <c r="C24">
         <v>511.37584442281513</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>11.52130206690908</v>
+        <v>11.430487979006177</v>
       </c>
       <c r="B25">
-        <v>-3.5791191244380882</v>
+        <v>-3.8259356526326269</v>
       </c>
       <c r="C25">
         <v>511.37584442281513</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>13.332922728003423</v>
+        <v>13.233663149430765</v>
       </c>
       <c r="B26">
-        <v>-4.4719882646099345</v>
+        <v>-4.7349351205780659</v>
       </c>
       <c r="C26">
         <v>511.37584442281513</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>15.139213870767469</v>
+        <v>15.032322901942445</v>
       </c>
       <c r="B27">
-        <v>-5.3767681847246038</v>
+        <v>-5.653653367104674</v>
       </c>
       <c r="C27">
         <v>511.37584442281513</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>16.940030414903333</v>
+        <v>16.82631840974722</v>
       </c>
       <c r="B28">
-        <v>-6.293783120368702</v>
+        <v>-6.5824107201833382</v>
       </c>
       <c r="C28">
         <v>511.37584442281513</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>18.735227280113122</v>
+        <v>18.615500846051095</v>
       </c>
       <c r="B29">
-        <v>-7.2233573071288371</v>
+        <v>-7.5215275077849526</v>
       </c>
       <c r="C29">
         <v>511.37584442281513</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>20.524737717258191</v>
+        <v>20.399802287539103</v>
       </c>
       <c r="B30">
-        <v>-8.16563992064388</v>
+        <v>-8.4711499249398212</v>
       </c>
       <c r="C30">
         <v>511.37584442281513</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>22.308808301836848</v>
+        <v>22.179478424812388</v>
       </c>
       <c r="B31">
-        <v>-9.1200798967617516</v>
+        <v>-9.43072763491594</v>
       </c>
       <c r="C31">
         <v>511.37584442281513</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>24.08776394050664</v>
+        <v>23.954865851951144</v>
       </c>
       <c r="B32">
-        <v>-10.085951111382656</v>
+        <v>-10.399536168040717</v>
       </c>
       <c r="C32">
         <v>511.37584442281513</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>25.861929539925121</v>
+        <v>25.726301163035536</v>
       </c>
       <c r="B33">
-        <v>-11.062527440406777</v>
+        <v>-11.376851054641557</v>
       </c>
       <c r="C33">
         <v>511.37584442281513</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>27.631503195138649</v>
+        <v>27.493990227495193</v>
       </c>
       <c r="B34">
-        <v>-12.049366167183415</v>
+        <v>-12.362229190792817</v>
       </c>
       <c r="C34">
         <v>511.37584442281513</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>29.396175754748871</v>
+        <v>29.25761601615752</v>
       </c>
       <c r="B35">
-        <v>-13.047158204858308</v>
+        <v>-13.356352935556629</v>
       </c>
       <c r="C35">
         <v>511.37584442281513</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>31.155511255746234</v>
+        <v>31.016730775199367</v>
       </c>
       <c r="B36">
-        <v>-14.0568778740263</v>
+        <v>-14.360186013742061</v>
       </c>
       <c r="C36">
         <v>511.37584442281513</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>32.909073735121233</v>
+        <v>32.770886750797615</v>
       </c>
       <c r="B37">
-        <v>-15.079499495282258</v>
+        <v>-15.374692150158209</v>
       </c>
       <c r="C37">
         <v>511.37584442281513</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>34.6561163804389</v>
+        <v>34.519315595321594</v>
       </c>
       <c r="B38">
-        <v>-16.116692097236207</v>
+        <v>-16.401525101033066</v>
       </c>
       <c r="C38">
         <v>511.37584442281513</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>36.394648981562753</v>
+        <v>36.259966585910682</v>
       </c>
       <c r="B39">
-        <v>-17.17290354055897</v>
+        <v>-17.445098748270425</v>
       </c>
       <c r="C39">
         <v>511.37584442281513</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>38.122370478930918</v>
+        <v>37.990468405896749</v>
       </c>
       <c r="B40">
-        <v>-18.253276393936563</v>
+        <v>-18.510517005192987</v>
       </c>
       <c r="C40">
         <v>511.37584442281513</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>39.83697981298149</v>
+        <v>39.708449738611662</v>
       </c>
       <c r="B41">
-        <v>-19.362953226054991</v>
+        <v>-19.602883785123467</v>
       </c>
       <c r="C41">
         <v>511.37584442281513</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>39.83697981298149</v>
+        <v>39.708449738611662</v>
       </c>
       <c r="B42">
-        <v>-19.362953226054991</v>
+        <v>-19.602883785123467</v>
       </c>
       <c r="C42">
         <v>511.37584442281513</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>38.013833071694641</v>
+        <v>37.878497404031549</v>
       </c>
       <c r="B43">
-        <v>-18.49584337523503</v>
+        <v>-18.751518258150575</v>
       </c>
       <c r="C43">
         <v>511.37584442281513</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>36.196214608385276</v>
+        <v>36.055254716197354</v>
       </c>
       <c r="B44">
-        <v>-17.616378542525148</v>
+        <v>-17.8857111950144</v>
       </c>
       <c r="C44">
         <v>511.37584442281513</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>34.381831741714649</v>
+        <v>34.236353927301167</v>
       </c>
       <c r="B45">
-        <v>-16.729682572372987</v>
+        <v>-17.010558827586543</v>
       </c>
       <c r="C45">
         <v>511.37584442281513</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>32.568391790343945</v>
+        <v>32.419427289535058</v>
       </c>
       <c r="B46">
-        <v>-15.840879309226185</v>
+        <v>-16.131157387738593</v>
       </c>
       <c r="C46">
         <v>511.37584442281513</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>30.753912629255602</v>
+        <v>30.602427525279698</v>
       </c>
       <c r="B47">
-        <v>-14.954398544566873</v>
+        <v>-15.251913341994795</v>
       </c>
       <c r="C47">
         <v>511.37584442281513</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>28.937654358716898</v>
+        <v>28.784589237670314</v>
       </c>
       <c r="B48">
-        <v>-14.071893858015276</v>
+        <v>-14.374474095490045</v>
       </c>
       <c r="C48">
         <v>511.37584442281513</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>27.119187635316255</v>
+        <v>26.965467500030677</v>
       </c>
       <c r="B49">
-        <v>-13.194324776226091</v>
+        <v>-13.499797288011855</v>
       </c>
       <c r="C49">
         <v>511.37584442281513</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>25.298083115642161</v>
+        <v>25.144617385684608</v>
       </c>
       <c r="B50">
-        <v>-12.322650825854042</v>
+        <v>-12.628840559347772</v>
       </c>
       <c r="C50">
         <v>511.37584442281513</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>23.474037942786442</v>
+        <v>23.321724554537866</v>
       </c>
       <c r="B51">
-        <v>-11.457548852678373</v>
+        <v>-11.762280480710924</v>
       </c>
       <c r="C51">
         <v>511.37584442281513</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>21.647255205854446</v>
+        <v>21.496997012823993</v>
       </c>
       <c r="B52">
-        <v>-10.598564978976457</v>
+        <v>-10.899669349016824</v>
       </c>
       <c r="C52">
         <v>511.37584442281513</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>19.818064480454886</v>
+        <v>19.6707733533585</v>
       </c>
       <c r="B53">
-        <v>-9.7449626461501921</v>
+        <v>-10.040278392606583</v>
       </c>
       <c r="C53">
         <v>511.37584442281513</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>17.98679534219648</v>
+        <v>17.843392168956861</v>
       </c>
       <c r="B54">
-        <v>-8.89600529560147</v>
+        <v>-9.1833788398213052</v>
       </c>
       <c r="C54">
         <v>511.37584442281513</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>16.153698723495452</v>
+        <v>16.015111015658402</v>
       </c>
       <c r="B55">
-        <v>-8.051132126033604</v>
+        <v>-8.3284163388453827</v>
       </c>
       <c r="C55">
         <v>511.37584442281513</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>14.31871098399815</v>
+        <v>14.185863302397651</v>
       </c>
       <c r="B56">
-        <v>-7.2104853653555807</v>
+        <v>-7.4755342172363379</v>
       </c>
       <c r="C56">
         <v>511.37584442281513</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>12.481689840158433</v>
+        <v>12.355501401332976</v>
       </c>
       <c r="B57">
-        <v>-6.3743829987777909</v>
+        <v>-6.6250502223949761</v>
       </c>
       <c r="C57">
         <v>511.37584442281513</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>10.642493008430163</v>
+        <v>10.523877684622731</v>
       </c>
       <c r="B58">
-        <v>-5.5431430115106313</v>
+        <v>-5.7772821017221023</v>
       </c>
       <c r="C58">
         <v>511.37584442281513</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>8.8009953309949314</v>
+        <v>8.6908622850689454</v>
       </c>
       <c r="B59">
-        <v>-4.7170451149915467</v>
+        <v>-4.9325093754229838</v>
       </c>
       <c r="C59">
         <v>511.37584442281513</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>6.9571401529453087</v>
+        <v>6.8563963780484247</v>
       </c>
       <c r="B60">
-        <v>-3.8962159255662057</v>
+        <v>-4.0908586549207628</v>
       </c>
       <c r="C60">
         <v>511.37584442281513</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5.1108879451015987</v>
+        <v>5.0204388995816549</v>
       </c>
       <c r="B61">
-        <v>-3.0807437858073285</v>
+        <v>-3.2524183244430449</v>
       </c>
       <c r="C61">
         <v>511.37584442281513</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3.2621991782841091</v>
+        <v>3.1829487856891236</v>
       </c>
       <c r="B62">
-        <v>-2.2707170382876343</v>
+        <v>-2.4172767682174361</v>
       </c>
       <c r="C62">
         <v>511.37584442281513</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.4111393586805519</v>
+        <v>1.3439934271759402</v>
       </c>
       <c r="B63">
-        <v>-1.4659892852018639</v>
+        <v>-1.5852889373634516</v>
       </c>
       <c r="C63">
         <v>511.37584442281513</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.44180586605177868</v>
+        <v>-0.4959259660143408</v>
       </c>
       <c r="B64">
-        <v>-0.66547516723282107</v>
+        <v>-0.75537605056822277</v>
       </c>
       <c r="C64">
         <v>511.37584442281513</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.2960458128881682</v>
+        <v>-2.3361997291535275</v>
       </c>
       <c r="B65">
-        <v>0.13214541531466564</v>
+        <v>0.073774106589204774</v>
       </c>
       <c r="C65">
         <v>511.37584442281513</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-4.15098979880391</v>
+        <v>-4.1762181975134371</v>
       </c>
       <c r="B66">
-        <v>0.92819256213576951</v>
+        <v>0.90347374852978768</v>
       </c>
       <c r="C66">
         <v>511.37584442281513</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-6.0068108425391591</v>
+        <v>-6.01615949019277</v>
       </c>
       <c r="B67">
-        <v>1.7222795988610169</v>
+        <v>1.7333394998683991</v>
       </c>
       <c r="C67">
         <v>511.37584442281513</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-7.8667367698935147</v>
+        <v>-7.8593528615977792</v>
       </c>
       <c r="B68">
-        <v>2.5071927548623427</v>
+        <v>2.556205625995573</v>
       </c>
       <c r="C68">
         <v>511.37584442281513</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-9.7332679407393261</v>
+        <v>-9.7083769744356214</v>
       </c>
       <c r="B69">
-        <v>3.2773440511946368</v>
+        <v>3.3665219314765493</v>
       </c>
       <c r="C69">
         <v>511.37584442281513</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-11.602940044180425</v>
+        <v>-11.55965698930947</v>
       </c>
       <c r="B70">
-        <v>4.0404757719031688</v>
+        <v>4.1719827367997055</v>
       </c>
       <c r="C70">
         <v>511.37584442281513</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-13.471976011307234</v>
+        <v>-13.409295329417795</v>
       </c>
       <c r="B71">
-        <v>4.805029174494301</v>
+        <v>4.9809770076527764</v>
       </c>
       <c r="C71">
         <v>511.37584442281513</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-15.341312411924973</v>
+        <v>-15.258256970444167</v>
       </c>
       <c r="B72">
-        <v>5.5689111473283495</v>
+        <v>5.7914277745977714</v>
       </c>
       <c r="C72">
         <v>511.37584442281513</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-17.212513076211216</v>
+        <v>-17.108153894277994</v>
       </c>
       <c r="B73">
-        <v>6.32862673345823</v>
+        <v>6.5998654816905606</v>
       </c>
       <c r="C73">
         <v>511.37584442281513</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-19.084937237118186</v>
+        <v>-18.95832355514689</v>
       </c>
       <c r="B74">
-        <v>7.0856079638532909</v>
+        <v>7.4077161620881817</v>
       </c>
       <c r="C74">
         <v>511.37584442281513</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-20.957380974233121</v>
+        <v>-20.807522343616085</v>
       </c>
       <c r="B75">
-        <v>7.8425454439709847</v>
+        <v>8.2176565037453386</v>
       </c>
       <c r="C75">
         <v>511.37584442281513</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-22.828592350908664</v>
+        <v>-22.654456923263066</v>
       </c>
       <c r="B76">
-        <v>8.60223708930477</v>
+        <v>9.0324702247062572</v>
       </c>
       <c r="C76">
         <v>511.37584442281513</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-24.697412465940769</v>
+        <v>-24.497929838120566</v>
       </c>
       <c r="B77">
-        <v>9.36727289323895</v>
+        <v>9.8547346743173421</v>
       </c>
       <c r="C77">
         <v>511.37584442281513</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-26.563102576133151</v>
+        <v>-26.337176881030036</v>
       </c>
       <c r="B78">
-        <v>10.139303850685185</v>
+        <v>10.686094697044219</v>
       </c>
       <c r="C78">
         <v>511.37584442281513</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-28.424402200524025</v>
+        <v>-28.170895510754729</v>
       </c>
       <c r="B79">
-        <v>10.921146972567845</v>
+        <v>11.529353822951421</v>
       </c>
       <c r="C79">
         <v>511.37584442281513</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-30.279098734166503</v>
+        <v>-29.996800760193235</v>
       </c>
       <c r="B80">
-        <v>11.717747143018944</v>
+        <v>12.389430110511519</v>
       </c>
       <c r="C80">
         <v>511.37584442281513</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-32.12175569214385</v>
+        <v>-31.809281654113445</v>
       </c>
       <c r="B81">
-        <v>12.541254198382532</v>
+        <v>13.278400365671848</v>
       </c>
       <c r="C81">
         <v>511.37584442281513</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-33.854446236566154</v>
+        <v>-33.5073107705237</v>
       </c>
       <c r="B82">
-        <v>13.610521878211719</v>
+        <v>14.413711381597436</v>
       </c>
       <c r="C82">
         <v>511.37584442281513</v>
